--- a/results/volare_full_iv/slides_tables.xlsx
+++ b/results/volare_full_iv/slides_tables.xlsx
@@ -14,9 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5_ex_tariff_shock" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T6_deciles_M_ALL_h1" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T7_scenarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T8_error_concentration" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T9_har_coefficients" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T10_variable_importance" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T7b_scenarios_unfiltered" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T8_error_concentration" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T9_har_coefficients" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T10_variable_importance" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,6 +843,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RVD_median</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RVW_median</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RVM_median</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>share_RVM_negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>HAR</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>with COVID</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.733</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>without 2020</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>HAR-X</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>with COVID</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.392</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>without 2020</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1286,7 +1425,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>0.842*</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -1306,7 +1445,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.746**</t>
+          <t>0.746*</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1775,7 +1914,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>0.898*</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -3361,7 +3500,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.861*</t>
+          <t>0.861</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3727,12 +3866,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.798***</t>
+          <t>0.798**</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>0.842*</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3752,12 +3891,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.746**</t>
+          <t>0.746*</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.692***</t>
+          <t>0.692**</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -4092,7 +4231,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.894*</t>
+          <t>0.894</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -4159,7 +4298,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.816*</t>
+          <t>0.816</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -4221,7 +4360,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>0.898*</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -4293,7 +4432,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>1.735**</t>
+          <t>1.735*</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -4397,7 +4536,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.896*</t>
+          <t>0.896</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -4427,7 +4566,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.764***</t>
+          <t>0.764**</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -4860,12 +4999,12 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.929*</t>
+          <t>0.928*</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>1.000</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -4875,27 +5014,27 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>0.986</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.387</t>
+          <t>1.432</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.915*</t>
+          <t>0.915</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.296</t>
+          <t>1.295</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>6.233</t>
+          <t>5.733</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -4917,7 +5056,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>0.955</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -4932,7 +5071,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>0.703</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -4942,7 +5081,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>0.842*</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -4952,7 +5091,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.888*</t>
+          <t>0.888</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -4962,7 +5101,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.506</t>
+          <t>1.040</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -4972,12 +5111,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.746**</t>
+          <t>0.746*</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>73.932</t>
+          <t>1.677</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -4992,7 +5131,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>17714511997.927</t>
+          <t>9.982</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5014,29 +5153,29 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>1.008</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.986</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.023</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.045</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>1.002</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.986</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>1.023</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1.061</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.002</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>1.027</t>
@@ -5059,7 +5198,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.982</t>
+          <t>1.005</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -5069,12 +5208,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.000</t>
+          <t>0.999</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.430</t>
+          <t>1.467</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -5084,12 +5223,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.328</t>
+          <t>1.327</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>6.342</t>
+          <t>5.794</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -5111,7 +5250,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1.024</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -5126,7 +5265,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.014</t>
+          <t>1.001</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5151,12 +5290,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>0.953</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>1.020</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -5166,27 +5305,27 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1.034</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.419</t>
+          <t>1.451</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.911*</t>
+          <t>0.911</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.307</t>
+          <t>1.306</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>6.254</t>
+          <t>5.761</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -5208,7 +5347,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.994</t>
+          <t>1.026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -5223,7 +5362,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>0.899</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5253,7 +5392,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.006</t>
+          <t>1.038</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -5268,7 +5407,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.181</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -5305,7 +5444,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>1.005</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -5320,7 +5459,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.652</t>
+          <t>0.711</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5350,7 +5489,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.035</t>
+          <t>1.068</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -5365,12 +5504,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.688</t>
+          <t>0.758</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.921*</t>
+          <t>0.921</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -5380,7 +5519,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>3.228</t>
+          <t>3.030</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -5402,7 +5541,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.963</t>
+          <t>0.992</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -5417,7 +5556,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.728</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5447,7 +5586,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.083</t>
+          <t>1.120</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -5462,7 +5601,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>0.825</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -5477,7 +5616,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>7.779</t>
+          <t>6.445</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5499,7 +5638,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.968</t>
+          <t>0.997</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -5514,7 +5653,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.649</t>
+          <t>0.708</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5544,7 +5683,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.031</t>
+          <t>1.064</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -5559,12 +5698,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.692</t>
+          <t>0.763</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0.919*</t>
+          <t>0.919</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -5574,7 +5713,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>5.784</t>
+          <t>5.191</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5596,7 +5735,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.631</t>
+          <t>1.690</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -5611,7 +5750,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>1.206</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5641,7 +5780,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>1.697</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5651,12 +5790,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>0.898*</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.200</t>
+          <t>1.356</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -5693,7 +5832,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.890</t>
+          <t>1.959</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -5708,7 +5847,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.287</t>
+          <t>1.465</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5738,7 +5877,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>1.504</t>
+          <t>1.556</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -5753,7 +5892,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.112</t>
+          <t>1.254</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -5790,7 +5929,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -5805,7 +5944,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>0.997</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5835,7 +5974,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1.722</t>
+          <t>1.773</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -5850,7 +5989,7 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.065</t>
+          <t>1.177</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -5887,7 +6026,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.256</t>
+          <t>1.294</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -5902,7 +6041,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.844</t>
+          <t>0.927</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -5932,7 +6071,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -5947,7 +6086,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.873</t>
+          <t>0.965</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -5992,132 +6131,1315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>window</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>share of HAR SSE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>share of test days</t>
-        </is>
-      </c>
+          <t>M_HAR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>M_ALL</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>h=1</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>h=5</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>h=22</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>h=1</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>h=5</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>h=22</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="n"/>
+      <c r="S2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Tariff shock Apr 2025</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>COVID in test</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>COVID Feb-May 2020</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>COVID in test</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tariff shock Apr 2025</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1%</t>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Without 2020</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tariff shock Apr 2025</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4%</t>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>HAR-X</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.929*</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.976</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.914**</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.987</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.387</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.915</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.296</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6.233</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.969</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>LogHAR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.921</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.927</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.932*</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.823*</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.635</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.946*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.842*</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.956</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.854**</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.506</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.855**</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.746*</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>73.932</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.872**</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>17714511997.927</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.941</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>LevHAR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.002</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.986</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.023</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.061</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.002</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.027</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.045</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.981</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.935</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.982</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.910**</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.430</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.328</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>6.342</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.958</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SHAR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.042</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.013</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.098</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.014</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.995</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.083</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.007</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.004</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.954</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.995</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.909**</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.035</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.419</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.911</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.307</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>6.254</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.969</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>HARQ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.032</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.994</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.960</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.169</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.993</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.254</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.067</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.970</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.946</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.006</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.908*</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.050</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.928</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.311</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.992</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.965</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.951</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.975</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.983</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.864*</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.652</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.003</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.935</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.007</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.988</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.908</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.035</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.784*</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.688</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.921</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0.897</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3.228</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.908</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.971</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.963</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.990</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.913</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.669</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.017</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.017</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.987</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.923**</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.083</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.939*</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.821*</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.744</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.923</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0.886</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>7.779</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.885</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Elastic net</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.954</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.968</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.987</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.867*</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.649</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.010</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.944</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.013</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.980</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.894**</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.031</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.933*</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.778*</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.919</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.876</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5.784</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Random forest</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.010</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.631</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.005</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.247</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1.067</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.990</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2.241</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.141</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.871</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.868**</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.960</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.898*</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.945</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.148</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.899</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gradient boosting</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.238</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.890</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.046</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.844</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1.287</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.029</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2.760</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.223</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.957</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1.504</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1.030</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.924</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.112</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.979</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.799</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.924</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Neural net (single)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.029</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.353</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.030</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.898</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.078</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.160</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.160</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.161</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.722</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1.053</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.938</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.027</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.247</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.174</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1.068</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Neural net (ensemble)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.965</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.256</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.015</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.038</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.098</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.099</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.118</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.915*</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.353</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1.001</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.809*</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.873</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0.932</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.114</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0.981</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="Q2:S2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6128,134 +7450,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>scenario</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RVD_median</t>
+          <t>window</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RVW_median</t>
+          <t>share of HAR SSE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>RVM_median</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>share_RVM_negative</t>
+          <t>share of test days</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>HAR</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>with COVID</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.049</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.733</v>
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tariff shock Apr 2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>without 2020</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>COVID Feb-May 2020</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>HAR-X</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>with COVID</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.392</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tariff shock Apr 2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>without 2020</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5669999999999999</v>
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tariff shock Apr 2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A2:A3"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/volare_full_iv/slides_tables.xlsx
+++ b/results/volare_full_iv/slides_tables.xlsx
@@ -8,16 +8,17 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T1_descriptives" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2_vs_paper_baseline" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3_pairwise_M_ALL_h1" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4_qlike_baseline" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5_ex_tariff_shock" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T6_deciles_M_ALL_h1" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T7_scenarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T7b_scenarios_unfiltered" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T8_error_concentration" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T9_har_coefficients" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T10_variable_importance" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T12_logrf_extension" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T2_vs_paper_baseline" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T3_pairwise_M_ALL_h1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T4_qlike_baseline" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T5_ex_tariff_shock" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T6_deciles_M_ALL_h1" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T7_scenarios" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T7b_scenarios_unfiltered" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T8_error_concentration" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T9_har_coefficients" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T10_variable_importance" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -843,134 +844,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>scenario</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>RVD_median</t>
+          <t>window</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>RVW_median</t>
+          <t>share of HAR SSE</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>RVM_median</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>share_RVM_negative</t>
+          <t>share of test days</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>HAR</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>with COVID</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.503</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-0.049</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.733</v>
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tariff shock Apr 2025</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n"/>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>without 2020</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.228</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.238</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.251</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>COVID Feb-May 2020</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>HAR-X</t>
-        </is>
-      </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>with COVID</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-0.392</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tariff shock Apr 2025</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n"/>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>without 2020</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-0.013</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.5669999999999999</v>
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tariff shock Apr 2025</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>4%</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A2:A3"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -981,6 +980,144 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>RVD_median</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>RVW_median</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>RVM_median</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>share_RVM_negative</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>HAR</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>with COVID</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-0.049</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.733</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n"/>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>without 2020</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.251</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>HAR-X</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>with COVID</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.392</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>without 2020</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1221,6 +1358,103 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>1 day</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>1 week</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>1 month</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Random forest</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>0.868**</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>0.898*</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.148</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Random forest on log RV</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>0.868**</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.765*</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.836</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>LogHAR</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0.854**</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.746*</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2149,13 +2383,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2224,6 +2458,11 @@
           <t>NN2_ens</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LogRF</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -2296,6 +2535,11 @@
           <t>0.915*</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.868**</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -2368,6 +2612,11 @@
           <t>0.989</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.939</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -2440,6 +2689,11 @@
           <t>1.073</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>1.018</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -2512,6 +2766,11 @@
           <t>0.985</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.934</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -2584,6 +2843,11 @@
           <t>0.967</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -2656,6 +2920,11 @@
           <t>0.977</t>
         </is>
       </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0.926</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -2728,6 +2997,11 @@
           <t>1.008</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0.956*</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -2800,6 +3074,11 @@
           <t>0.992</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0.941*</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -2872,6 +3151,11 @@
           <t>1.023</t>
         </is>
       </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.971</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -2944,6 +3228,11 @@
           <t>1.056</t>
         </is>
       </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>1.002</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -3016,6 +3305,11 @@
           <t>1.008</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.956</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -3088,6 +3382,11 @@
           <t>0.922*</t>
         </is>
       </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.877**</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -3156,6 +3455,88 @@
         </is>
       </c>
       <c r="N14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.954*</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>LogRF</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.160</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.075</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.986</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.083</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1.105</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.096</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.050</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.068</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.033</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.002</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.098</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1.153</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1.053</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3166,7 +3547,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3666,7 +4047,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4595,7 +4976,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4806,13 +5187,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5014,12 +5395,12 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>0.987</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>1.432</t>
+          <t>1.427</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -5029,12 +5410,12 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>1.295</t>
+          <t>1.292</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>5.733</t>
+          <t>1.975</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -5066,12 +5447,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.823*</t>
+          <t>0.825*</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>0.870</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5081,12 +5462,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.842*</t>
+          <t>0.844*</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.956</t>
+          <t>0.963</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -5111,12 +5492,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.746*</t>
+          <t>0.748*</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>1.677</t>
+          <t>1.227</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -5126,12 +5507,12 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>0.833</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>9.982</t>
+          <t>1.631</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -5168,7 +5549,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1.032</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5178,12 +5559,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.027</t>
+          <t>1.028</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1.043</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -5213,7 +5594,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1.445</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -5223,12 +5604,12 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.327</t>
+          <t>1.323</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>5.794</t>
+          <t>1.996</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -5265,24 +5646,24 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>1.006</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.995</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.083</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>1.001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.995</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.083</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.007</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>1.004</t>
@@ -5305,12 +5686,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>1.034</t>
+          <t>1.035</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>1.451</t>
+          <t>1.428</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -5320,12 +5701,12 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>1.303</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>5.761</t>
+          <t>1.974</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -5357,12 +5738,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.169</t>
+          <t>1.172</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.899</t>
+          <t>1.126</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -5372,12 +5753,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1.255</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>1.076</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -5402,12 +5783,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>1.050</t>
+          <t>1.053</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>1.181</t>
+          <t>1.479</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -5417,12 +5798,12 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>1.311</t>
+          <t>1.312</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1.992</t>
+          <t>2.007</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -5454,12 +5835,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.864*</t>
+          <t>0.866*</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.711</t>
+          <t>0.879</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5469,12 +5850,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>0.937</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1.017</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -5499,12 +5880,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.784*</t>
+          <t>0.785*</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.758</t>
+          <t>0.942</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -5514,12 +5895,12 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>0.899</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>3.030</t>
+          <t>1.607</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -5551,12 +5932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.913</t>
+          <t>0.915</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.728</t>
+          <t>0.892</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5571,7 +5952,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>1.020</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -5596,12 +5977,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.821*</t>
+          <t>0.822*</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.825</t>
+          <t>1.029</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -5611,12 +5992,12 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.886</t>
+          <t>0.888</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>6.445</t>
+          <t>1.948</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5648,12 +6029,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.867*</t>
+          <t>0.869*</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0.708</t>
+          <t>0.869</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5663,12 +6044,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.944</t>
+          <t>0.946</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1.018</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -5693,12 +6074,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>0.778*</t>
+          <t>0.780*</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0.763</t>
+          <t>0.950</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -5708,12 +6089,12 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>0.876</t>
+          <t>0.877</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>5.191</t>
+          <t>1.861</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5745,12 +6126,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.247</t>
+          <t>1.250</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1.206</t>
+          <t>1.529</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5760,12 +6141,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2.241</t>
+          <t>2.244</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>1.151</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -5790,12 +6171,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0.898*</t>
+          <t>0.900*</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>1.356</t>
+          <t>1.706</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -5805,12 +6186,12 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>1.148</t>
+          <t>1.150</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1.518</t>
+          <t>1.530</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5842,12 +6223,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.844</t>
+          <t>1.848</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1.465</t>
+          <t>1.863</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5857,12 +6238,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2.760</t>
+          <t>2.730</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.223</t>
+          <t>1.229</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -5887,12 +6268,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>1.924</t>
+          <t>1.926</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1.569</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -5902,12 +6283,12 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.904</t>
+          <t>0.905</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1.799</t>
+          <t>1.814</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -5939,12 +6320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>0.993</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.997</t>
+          <t>1.243</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -5954,12 +6335,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1.160</t>
+          <t>1.162</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.160</t>
+          <t>1.176</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -5984,12 +6365,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.938</t>
+          <t>0.940</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>1.177</t>
+          <t>1.397</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -5999,12 +6380,12 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>1.247</t>
+          <t>1.246</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>1.184</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -6036,12 +6417,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.914</t>
+          <t>0.916</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>1.149</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6051,12 +6432,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.098</t>
+          <t>1.100</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1.109</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -6081,12 +6462,12 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>0.809*</t>
+          <t>0.811*</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>0.965</t>
+          <t>1.193</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -6096,12 +6477,12 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>0.932</t>
+          <t>0.934</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1.114</t>
+          <t>1.105</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -6110,1322 +6491,100 @@
         </is>
       </c>
     </row>
-  </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="E2:G2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="N2:P2"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="B1:J1"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="Q2:S2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr"/>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>M_HAR</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="n"/>
-      <c r="D1" s="1" t="n"/>
-      <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
-      <c r="G1" s="1" t="n"/>
-      <c r="H1" s="1" t="n"/>
-      <c r="I1" s="1" t="n"/>
-      <c r="J1" s="1" t="n"/>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>M_ALL</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="n"/>
-      <c r="M1" s="1" t="n"/>
-      <c r="N1" s="1" t="n"/>
-      <c r="O1" s="1" t="n"/>
-      <c r="P1" s="1" t="n"/>
-      <c r="Q1" s="1" t="n"/>
-      <c r="R1" s="1" t="n"/>
-      <c r="S1" s="1" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr"/>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>h=1</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>h=5</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>h=22</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t>h=1</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t>h=5</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="n"/>
-      <c r="P2" s="1" t="n"/>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t>h=22</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="n"/>
-      <c r="S2" s="1" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr"/>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="inlineStr">
-        <is>
-          <t>COVID in test</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="inlineStr">
-        <is>
-          <t>Without 2020</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>COVID in test</t>
-        </is>
-      </c>
-      <c r="G3" s="1" t="inlineStr">
-        <is>
-          <t>Without 2020</t>
-        </is>
-      </c>
-      <c r="H3" s="1" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I3" s="1" t="inlineStr">
-        <is>
-          <t>COVID in test</t>
-        </is>
-      </c>
-      <c r="J3" s="1" t="inlineStr">
-        <is>
-          <t>Without 2020</t>
-        </is>
-      </c>
-      <c r="K3" s="1" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="L3" s="1" t="inlineStr">
-        <is>
-          <t>COVID in test</t>
-        </is>
-      </c>
-      <c r="M3" s="1" t="inlineStr">
-        <is>
-          <t>Without 2020</t>
-        </is>
-      </c>
-      <c r="N3" s="1" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="O3" s="1" t="inlineStr">
-        <is>
-          <t>COVID in test</t>
-        </is>
-      </c>
-      <c r="P3" s="1" t="inlineStr">
-        <is>
-          <t>Without 2020</t>
-        </is>
-      </c>
-      <c r="Q3" s="1" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="R3" s="1" t="inlineStr">
-        <is>
-          <t>COVID in test</t>
-        </is>
-      </c>
-      <c r="S3" s="1" t="inlineStr">
-        <is>
-          <t>Without 2020</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>HAR-X</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.929*</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.976</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.914**</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.987</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>1.387</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0.915</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>1.296</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>6.233</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.969</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>LogHAR</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>0.921</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>0.927</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>0.932*</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0.823*</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>0.635</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.946*</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.842*</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.956</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>0.888</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.854**</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>1.506</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.855**</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.746*</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>73.932</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>0.872**</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0.832</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>17714511997.927</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0.941</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>LevHAR</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.003</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1.002</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>0.986</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>RF + LogHAR (50/50)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.942</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.204</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>0.951</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0.955</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1.089</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0.946</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>1.289</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
         <is>
           <t>1.023</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1.061</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1.002</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.027</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1.045</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.981</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.935</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>0.982</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>0.910**</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>1.430</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0.917</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>1.328</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>6.342</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0.958</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>SHAR</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.042</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1.013</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>0.991</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1.098</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>1.014</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.995</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.083</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1.007</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>1.004</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.954</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>0.995</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>0.909**</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>1.035</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>1.419</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>0.911</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1.307</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>6.254</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0.969</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>HARQ</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.032</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>0.994</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>0.960</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>1.169</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0.811</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0.993</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.254</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1.067</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>0.970</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.946</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1.006</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.908*</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>1.050</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>1.065</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0.928</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1.311</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>1.992</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0.965</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>Ridge</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>0.951</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.975</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>0.983</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0.864*</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0.652</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>1.003</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.935</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1.007</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>0.988</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.908</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.035</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>0.933</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0.784*</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0.688</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0.921</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0.897</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>3.228</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0.908</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>Lasso</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>0.971</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.963</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>0.990</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0.913</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>0.669</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>1.017</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.991</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.017</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>0.987</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.923**</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>1.083</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>0.939*</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>0.821*</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>0.744</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>0.923</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>0.886</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>7.779</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0.885</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Elastic net</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>0.954</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>0.968</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>0.987</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0.867*</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>0.649</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>1.010</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.944</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1.013</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>0.980</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.894**</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.031</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>0.933*</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>0.778*</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>0.692</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>0.919</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>0.876</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>5.784</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0.884</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>Random forest</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.010</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1.631</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.005</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>1.247</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>1.067</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0.990</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2.241</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1.141</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>0.871</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.868**</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>1.639</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>0.960</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>0.898*</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>1.200</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>0.945</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>1.148</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>1.518</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>0.899</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Gradient boosting</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.238</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1.890</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.046</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>1.844</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>1.287</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>1.029</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2.760</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1.223</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>0.933</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.957</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>1.504</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>1.030</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>1.924</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>1.112</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>0.979</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>0.904</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>1.799</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0.924</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Neural net (single)</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.029</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1.353</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.030</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0.991</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>0.898</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>1.078</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1.160</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1.160</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>1.161</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>1.000</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>1.722</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>1.053</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>0.938</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>1.065</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>1.027</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>1.247</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>1.174</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>1.068</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Neural net (ensemble)</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>0.965</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1.256</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.015</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.914</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>0.844</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>1.038</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>1.098</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1.099</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>1.118</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.915*</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>1.353</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>1.001</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>0.809*</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>0.873</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>0.991</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>0.932</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>1.114</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0.981</t>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.841</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0.845**</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0.887</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>0.887**</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0.786*</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0.998</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>0.882*</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>0.918</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1.362</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0.846</t>
         </is>
       </c>
     </row>
@@ -7450,132 +6609,1340 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
+      <c r="A1" s="1" t="inlineStr"/>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>window</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>share of HAR SSE</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>share of test days</t>
-        </is>
-      </c>
+          <t>M_HAR</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>M_ALL</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+      <c r="S1" s="1" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr"/>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>h=1</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>h=5</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>h=22</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>h=1</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>h=5</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>h=22</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="n"/>
+      <c r="S2" s="1" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr"/>
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Tariff shock Apr 2025</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" s="1" t="inlineStr">
         <is>
           <t>COVID in test</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>COVID Feb-May 2020</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>COVID in test</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tariff shock Apr 2025</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>12%</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>1%</t>
+      <c r="G3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="M3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>Baseline</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>COVID in test</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>Without 2020</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Without 2020</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tariff shock Apr 2025</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>4%</t>
-        </is>
-      </c>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>HAR-X</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.929*</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.976</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.914**</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.987</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>1.387</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0.915</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1.296</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>6.233</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.969</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>LogHAR</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.921</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>0.927</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.932*</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.823*</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0.635</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.946*</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.842*</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.956</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.888</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.854**</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>1.506</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.855**</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0.746*</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>73.932</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0.872**</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0.832</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>17714511997.927</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0.941</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>LevHAR</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.003</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1.002</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0.986</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1.023</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.061</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1.002</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1.027</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1.045</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.981</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.935</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.982</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.910**</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>1.430</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0.917</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>1.328</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>6.342</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0.958</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SHAR</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.042</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1.013</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1.098</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.014</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.995</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1.083</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1.007</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>1.004</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.954</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.995</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.909**</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.035</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>1.419</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0.911</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>1.307</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>6.254</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0.969</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>HARQ</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.032</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.994</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0.960</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1.169</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0.811</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.993</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.254</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1.067</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.970</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.946</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1.006</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.908*</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.050</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0.928</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1.311</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1.992</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0.965</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Ridge</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.951</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.975</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>0.983</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0.864*</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0.652</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1.003</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.935</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1.007</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.988</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.908</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1.035</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0.784*</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0.688</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0.921</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0.897</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>3.228</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0.908</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Lasso</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.971</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.963</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0.990</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0.913</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0.669</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.017</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.017</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.987</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.923**</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>1.083</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.939*</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0.821*</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0.744</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>0.923</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>0.886</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>7.779</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0.885</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Elastic net</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.954</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>0.968</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0.987</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0.867*</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0.649</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1.010</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.944</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1.013</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.980</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.894**</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>1.031</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.933*</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.778*</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0.692</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>0.919</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>0.876</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>5.784</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0.884</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Random forest</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.010</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.631</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.005</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.247</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1.067</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.990</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2.241</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1.141</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.871</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.868**</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>1.639</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.960</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.898*</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>1.200</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.945</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1.148</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1.518</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.899</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gradient boosting</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.238</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1.890</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.046</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.844</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1.287</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1.029</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2.760</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1.223</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.957</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>1.504</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>1.030</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>1.924</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>1.112</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.979</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.904</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1.799</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.924</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Neural net (single)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.029</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.353</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.030</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.898</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1.078</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>1.160</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.160</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>1.161</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1.000</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1.722</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1.053</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.938</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1.065</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1.027</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1.247</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1.174</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1.068</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Neural net (ensemble)</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.965</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.256</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.015</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0.914</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>0.844</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1.038</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1.098</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1.099</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>1.118</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0.915*</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1.353</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>1.001</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0.809*</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0.873</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>0.991</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>0.932</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1.114</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0.981</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>RF + LogHAR (50/50)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
     </row>
   </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="N2:P2"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="B1:J1"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="Q2:S2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>